--- a/output/2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -562,7 +562,6 @@
           <t>VAMAG Valjevo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Valjevo, Kolubarski</t>
@@ -578,7 +577,6 @@
           <t>062/415-906</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Macchine edili e utensili (vendita). Confermato su directory B2B locale (planplus.rs): "VAMAG Valjevo - gradjevinske masine i alati", Radnicka 3, 14000 Valjevo, telefono corrispondente.</t>
@@ -586,7 +584,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -596,7 +594,6 @@
           <t>Woby Haus (prodaja masina i alata)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Valjevo, Kolubarski</t>
@@ -612,7 +609,6 @@
           <t>014/230-121</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Vendita macchine e utensili. Confermato su directory B2B locale (planplus.rs): Uzun Mirkova 2B, 14000 Valjevo, telefono corrispondente, aperto tutti i giorni 10:00-22:00.</t>
@@ -620,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -630,7 +626,6 @@
           <t>Sinbo - STIHL prodaja</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Lajkovac, Kolubarski</t>
@@ -646,7 +641,6 @@
           <t>014/343-3533</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Dealer ufficiale STIHL/Villager/AGM/Black&amp;Decker/DeWalt/Gardena. Confermato su directory B2B locale (planplus.rs) e profilo aziendale ekapija.com: Vojvode Misica 63, 14224 Lajkovac; partner STIHL dal 2015; attivita' dichiarata retail e wholesale su 5 punti vendita (Lazarevac, Lajkovac, Valjevo, Ub) piu' centro assistenza.</t>
@@ -654,7 +648,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
